--- a/2024AIDataScienceGNRClub/Advanced Excel/jan25.xlsx
+++ b/2024AIDataScienceGNRClub/Advanced Excel/jan25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D97549-8171-4045-A4FB-37EBE0427D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D8A546-A860-4FE0-A7A5-F3FCEBC76B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{8841A449-B5A4-4350-BFCF-745781B78CE1}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Data Validation" sheetId="2" r:id="rId1"/>
     <sheet name="Population" sheetId="3" r:id="rId2"/>
     <sheet name="Per Capita Income" sheetId="4" r:id="rId3"/>
+    <sheet name="HLookup &amp; Transpose" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
   <si>
     <t>Qty:</t>
   </si>
@@ -92,9 +93,6 @@
     <t>Enter Index No</t>
   </si>
   <si>
-    <t>Index No</t>
-  </si>
-  <si>
     <t>Enter Row No</t>
   </si>
   <si>
@@ -110,20 +108,83 @@
     <t>Parameter</t>
   </si>
   <si>
-    <t>Direct Value</t>
-  </si>
-  <si>
     <t>City:</t>
   </si>
   <si>
     <t>Mon</t>
+  </si>
+  <si>
+    <t>Not Possible using VLOOKUP!</t>
+  </si>
+  <si>
+    <t>VLOOKUP Exercise</t>
+  </si>
+  <si>
+    <t>Avg.Literacy</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>SR Tendulkar</t>
+  </si>
+  <si>
+    <t>V Sehwag</t>
+  </si>
+  <si>
+    <t>V Kohli</t>
+  </si>
+  <si>
+    <t>Matches</t>
+  </si>
+  <si>
+    <t>100's</t>
+  </si>
+  <si>
+    <t>50's</t>
+  </si>
+  <si>
+    <t>6's</t>
+  </si>
+  <si>
+    <t>4s</t>
+  </si>
+  <si>
+    <t>Batsman</t>
+  </si>
+  <si>
+    <t>Index No (row no)</t>
+  </si>
+  <si>
+    <t>Index No (col no)</t>
+  </si>
+  <si>
+    <t>Match only supports 1D arrays.</t>
+  </si>
+  <si>
+    <t>Index also supports 2D arrays.</t>
+  </si>
+  <si>
+    <t>Vlookup Value</t>
+  </si>
+  <si>
+    <t>Index-Match Value</t>
+  </si>
+  <si>
+    <t>City's row number</t>
+  </si>
+  <si>
+    <t>Parameter's col no</t>
+  </si>
+  <si>
+    <t>Index-Match Merged</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,8 +206,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -171,8 +253,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -215,29 +315,126 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E2F3"/>
+          <bgColor rgb="FFD9E2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E2F3"/>
+          <bgColor rgb="FFD9E2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Question Hlookupworked-style" pivot="0" count="3" xr9:uid="{4962AF0F-B938-41E4-B022-6C37AF0F05A8}">
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+    </tableStyle>
+  </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="FF336699"/>
+      <color rgb="FF0066CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -247,6 +444,18 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{052FC5AD-5931-438C-B43D-3E25C3F6271E}" name="Table_57" displayName="Table_57" ref="B3:E8" headerRowDxfId="0">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{5EEF02E1-7BA3-4C39-A4AF-BEF530C8566D}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{861E77EF-B067-4E98-A85B-76F7E182A4CB}" name="SR Tendulkar"/>
+    <tableColumn id="3" xr3:uid="{6797B327-F1BF-4CA4-B39E-B99C19FC350C}" name="V Sehwag"/>
+    <tableColumn id="4" xr3:uid="{F2982CA4-8082-4798-93BA-C6E1827628D1}" name="V Kohli"/>
+  </tableColumns>
+  <tableStyleInfo name="Question Hlookupworked-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -565,7 +774,7 @@
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="6">
         <v>15</v>
       </c>
       <c r="E3" s="1"/>
@@ -575,7 +784,7 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>10.5</v>
       </c>
       <c r="E4" s="1"/>
@@ -585,8 +794,8 @@
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>29</v>
+      <c r="D5" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -595,15 +804,15 @@
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="6"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="8"/>
+        <v>26</v>
+      </c>
+      <c r="D7" s="6"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -802,17 +1011,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32702AAF-D203-49B6-B2C2-C7513BD0F1DC}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -831,8 +1043,11 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -843,8 +1058,19 @@
         <f>VLOOKUP(A2, Population!$B$2:$D$7, 3,FALSE)</f>
         <v>68.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <f>VLOOKUP(A2, Population!$B$2:$C$7,2,FALSE)</f>
+        <v>86</v>
+      </c>
+      <c r="E2">
+        <f>VLOOKUP(A2, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>75.53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -855,8 +1081,20 @@
         <f>VLOOKUP(A3, Population!$B$2:$D$7, 3,FALSE)</f>
         <v>68.8</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <f>VLOOKUP(A3, Population!$B$2:$C$7,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <f>VLOOKUP(A3, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>40</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -867,8 +1105,24 @@
         <f>VLOOKUP(A4, Population!$B$2:$D$7, 3,FALSE)</f>
         <v>64.900000000000006</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <f>VLOOKUP(A4, Population!$B$2:$C$7,2,FALSE)</f>
+        <v>1.5</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP(A4, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>38.799999999999997</v>
+      </c>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -879,8 +1133,25 @@
         <f>VLOOKUP(A5, Population!$B$2:$D$7, 3,FALSE)</f>
         <v>72.3</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <f>VLOOKUP(A5, Population!$B$2:$C$7,2,FALSE)</f>
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(A5, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>61.05</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9">
+        <f>IFERROR(VLOOKUP(J4, A2:B7, 2, FALSE), "City not selected…")</f>
+        <v>2530</v>
+      </c>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -891,8 +1162,22 @@
         <f>VLOOKUP(A6, Population!$B$2:$D$7, 3,FALSE)</f>
         <v>52.2</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <f>VLOOKUP(A6, Population!$B$2:$C$7,2,FALSE)</f>
+        <v>46</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(A6, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>34.700000000000003</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -903,123 +1188,333 @@
         <f>VLOOKUP(A7, Population!$B$2:$D$7, 3,FALSE)</f>
         <v>60.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="D7">
+        <f>VLOOKUP(A7, Population!$B$2:$C$7,2,FALSE)</f>
+        <v>80</v>
+      </c>
+      <c r="E7">
+        <f>VLOOKUP(A7, Population!$B$2:$F$7, 5, FALSE)</f>
+        <v>62.2</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H8" s="8"/>
+      <c r="I8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="D11" s="2" t="s">
+      <c r="B11" s="7"/>
+      <c r="D11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E11" s="7"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
       </c>
       <c r="E15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="B16">
+        <f>MATCH(B15, A2:A7, 0)</f>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E16" t="str">
+        <f>INDEX(A2:A7, E15)</f>
+        <v>Surat</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D17" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
       <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19">
+        <f>MATCH(B18, A1:E1, 0)</f>
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
         <v>22</v>
       </c>
-      <c r="E18">
+      <c r="E19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20">
+        <f>INDEX(A2:E7, E18, E19)</f>
+        <v>61.05</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="F24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24">
+        <f>MATCH(C24, A2:A7, 0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="D25" s="2"/>
+      <c r="F25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25">
+        <f>MATCH(C25, A1:E1, 0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="17">
+        <f>INDEX(A2:E7, G24, G25)</f>
+        <v>46</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="17"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="D11:E11"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C25" xr:uid="{FE11E48D-BC8E-4AD7-96F3-F308073CC172}">
       <formula1>$A$1:$D$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C24" xr:uid="{D1AF33DB-32AB-4D38-869B-BE134C3B46C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C24 J4 B15" xr:uid="{D1AF33DB-32AB-4D38-869B-BE134C3B46C2}">
       <formula1>$A$2:$A$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18" xr:uid="{164EC93F-871D-41DF-9C1E-70006FCA150B}">
+      <formula1>$B$1:$E$1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A5EB3AB-EDCB-4C4F-89B8-2F0BD2EA93E2}">
+  <dimension ref="B3:E13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="10">
+        <v>200</v>
+      </c>
+      <c r="D4" s="10">
+        <v>97</v>
+      </c>
+      <c r="E4" s="10">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="10">
+        <v>20</v>
+      </c>
+      <c r="D5" s="10">
+        <v>22</v>
+      </c>
+      <c r="E5" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="10">
+        <v>32</v>
+      </c>
+      <c r="D6" s="10">
+        <v>35</v>
+      </c>
+      <c r="E6" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="10">
+        <v>100</v>
+      </c>
+      <c r="D7" s="10">
+        <v>25</v>
+      </c>
+      <c r="E7" s="10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="10">
+        <v>125</v>
+      </c>
+      <c r="D8" s="10">
+        <v>20</v>
+      </c>
+      <c r="E8" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="15"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="15"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/2024AIDataScienceGNRClub/Advanced Excel/jan25.xlsx
+++ b/2024AIDataScienceGNRClub/Advanced Excel/jan25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D8A546-A860-4FE0-A7A5-F3FCEBC76B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE5D10F-6BDD-441D-9D2A-8140D9F7BC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{8841A449-B5A4-4350-BFCF-745781B78CE1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{8841A449-B5A4-4350-BFCF-745781B78CE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Validation" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
   <si>
     <t>Qty:</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>Index-Match Merged</t>
+  </si>
+  <si>
+    <t>Row No:</t>
   </si>
 </sst>
 </file>
@@ -350,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -358,11 +361,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -371,6 +370,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1063,7 +1065,7 @@
         <v>86</v>
       </c>
       <c r="E2">
-        <f>VLOOKUP(A2, Population!$B$2:$F$7, 5, FALSE)</f>
+        <f>VLOOKUP(A2, Population!B2:F7,5,FALSE)</f>
         <v>75.53</v>
       </c>
       <c r="F2" t="s">
@@ -1089,10 +1091,10 @@
         <f>VLOOKUP(A3, Population!$B$2:$F$7, 5, FALSE)</f>
         <v>40</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1113,14 +1115,14 @@
         <f>VLOOKUP(A4, Population!$B$2:$F$7, 5, FALSE)</f>
         <v>38.799999999999997</v>
       </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8" t="s">
+      <c r="H4" s="7"/>
+      <c r="I4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="8"/>
+      <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1141,15 +1143,15 @@
         <f>VLOOKUP(A5, Population!$B$2:$F$7, 5, FALSE)</f>
         <v>61.05</v>
       </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8" t="s">
+      <c r="H5" s="7"/>
+      <c r="I5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="6">
         <f>IFERROR(VLOOKUP(J4, A2:B7, 2, FALSE), "City not selected…")</f>
         <v>2530</v>
       </c>
-      <c r="K5" s="8"/>
+      <c r="K5" s="7"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1170,12 +1172,12 @@
         <f>VLOOKUP(A6, Population!$B$2:$F$7, 5, FALSE)</f>
         <v>34.700000000000003</v>
       </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8" t="s">
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="8"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1196,36 +1198,36 @@
         <f>VLOOKUP(A7, Population!$B$2:$F$7, 5, FALSE)</f>
         <v>62.2</v>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="8"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H8" s="8"/>
-      <c r="I8" s="8" t="s">
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="8"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="D11" s="7" t="s">
+      <c r="B11" s="16"/>
+      <c r="D11" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="16"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1258,7 +1260,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="14" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1301,7 +1303,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="14" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1341,7 +1343,7 @@
         <v>48</v>
       </c>
       <c r="G25">
-        <f>MATCH(C25, A1:E1, 0)</f>
+        <f>MATCH(C25, A1:F1,0)</f>
         <v>4</v>
       </c>
     </row>
@@ -1358,8 +1360,8 @@
       <c r="B27" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="17">
-        <f>INDEX(A2:E7, G24, G25)</f>
+      <c r="C27" s="15">
+        <f>INDEX(A2:F7, G24, G25)</f>
         <v>46</v>
       </c>
       <c r="D27" s="2"/>
@@ -1369,7 +1371,10 @@
       <c r="B28" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="17"/>
+      <c r="C28" s="15">
+        <f>INDEX(A2:F7, MATCH(C24, A2:A7, 0), MATCH(C25,A1:F1,0))</f>
+        <v>46</v>
+      </c>
       <c r="D28" s="2"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1383,7 +1388,7 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="D11:E11"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C25" xr:uid="{FE11E48D-BC8E-4AD7-96F3-F308073CC172}">
       <formula1>$A$1:$D$1</formula1>
     </dataValidation>
@@ -1400,118 +1405,140 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A5EB3AB-EDCB-4C4F-89B8-2F0BD2EA93E2}">
-  <dimension ref="B3:E13"/>
+  <dimension ref="B3:F13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="14" t="s">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="10" t="s">
+    <row r="4" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="8">
         <v>200</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="8">
         <v>97</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="10" t="s">
+    <row r="5" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="8">
         <v>20</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>22</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="10" t="s">
+    <row r="6" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="8">
         <v>32</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="8">
         <v>35</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="8">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="10" t="s">
+    <row r="7" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="8">
         <v>100</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="8">
         <v>25</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="8">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="10" t="s">
+    <row r="8" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="8">
         <v>125</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="8">
         <v>20</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="8">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="15"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="12" t="s">
+      <c r="C11" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="15"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="13" t="s">
+      <c r="C12" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <f>MATCH(C12, Table_57[[#All],[Name]], 0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="15"/>
+      <c r="C13" s="13">
+        <f>HLOOKUP(C11, Table_57[[#All],[SR Tendulkar]:[V Kohli]], F12, FALSE)</f>
+        <v>200</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11" xr:uid="{CEFDEE61-DB96-47A1-ADB9-E1DBA72E17E4}">
+      <formula1>$C$3:$E$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{6771DEDD-F55B-45AD-ABDE-44C690A33272}">
+      <formula1>$B$4:$B$8</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
